--- a/ai_logs/Hung_ai_AuditLog.xlsx
+++ b/ai_logs/Hung_ai_AuditLog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS TUF\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS TUF\Downloads\Documents\LAB\shopeeconsole\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFB75BE-F505-465D-BED6-DC483A74BDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12ABD5D6-921F-4A23-B953-0507A79B36C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="160">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -221,7 +218,7 @@
 Decision: Designed BaseEntity to only hold getId() and toCsvLine() for subclasses to implement. The actual conversion of CSV rows back to objects is handled by specific repositories via the parseLine method.</t>
   </si>
   <si>
-    <t xml:space="preserve">BaseEntity.java, CsvRepository.java </t>
+    <t>BaseEntity.java, CsvRepository.java</t>
   </si>
   <si>
     <t>Optimizing the Generic Repository to avoid duplicate code for each entity during CSV read/write operations.</t>
@@ -278,7 +275,7 @@
 Decision: Implemented the NO_LOCK flow where checkout succeeds if the read stock value is valid at read-time, ignoring concurrent writes. Saved simulator logs to generate the race_condition_flow.png diagram.</t>
   </si>
   <si>
-    <t>transactions.csv and simulator output showing negative stock</t>
+    <t>transactions.csv, race_condition_flow.png</t>
   </si>
   <si>
     <t>VERIFICATION</t>
@@ -299,9 +296,6 @@
 Decision: Declared ReentrantReadWriteLock rwLock in CsvRepository. Wrapped findAll() with readLock and save()/update()/deleteById() with writeLock.</t>
   </si>
   <si>
-    <t xml:space="preserve">CsvRepository.java </t>
-  </si>
-  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -326,61 +320,61 @@
     <t>Corrective Action</t>
   </si>
   <si>
+    <t>Logic Error</t>
+  </si>
+  <si>
+    <t>AI suggested declaring fromCsvLine(String csv) as an abstract static method inside the abstract BaseEntity class, claiming that each subclass could override this static method for CSV deserialization.</t>
+  </si>
+  <si>
+    <t>Static methods in Java cannot be abstract or overridden by subclasses. Declaring a static abstract method causes a compile error: "illegal combination of modifiers: abstract and static".</t>
+  </si>
+  <si>
+    <t>Attempted to compile BaseEntity with the abstract static method as suggested; compiler immediately threw an error. Confirmed via official Java SE 17 Language Specification.</t>
+  </si>
+  <si>
+    <t>Redesigned the architecture: removed fromCsvLine() from BaseEntity entirely. Moved CSV row parsing into a protected abstract T parseLine(String line) method within the generic CsvRepository&lt;T&gt;, implemented separately by each concrete repository.</t>
+  </si>
+  <si>
+    <t>Oversimplification</t>
+  </si>
+  <si>
+    <t>AI suggested using Files.writeString(path, content, StandardOpenOption.APPEND) directly in a multi-threaded context and asserted that the OS would automatically queue writes safely without locks.</t>
+  </si>
+  <si>
+    <t>Writing concurrently without locking using APPEND causes interleaved lines, data corruption, and malformed CSV rows.</t>
+  </si>
+  <si>
+    <t>Ran simulation with 100 concurrent threads and inspected the output CSV, finding truncated lines and corrupted headers.</t>
+  </si>
+  <si>
+    <t>Implemented ReentrantReadWriteLock in CsvRepository to ensure only one thread can perform file write operations at a time.</t>
+  </si>
+  <si>
+    <t>AI suggested resolving the NO_LOCK race condition by adding a basic if (stock &gt; 0) check before checkout and claimed this made the code thread-safe.</t>
+  </si>
+  <si>
+    <t>A simple if statement is not atomic. Multiple threads can read stock = 1 simultaneously, pass the check, and concurrently subtract stock, causing negative inventory.</t>
+  </si>
+  <si>
+    <t>Ran simulator with 500 threads and observed a final stock of -19 despite having the check in place.</t>
+  </si>
+  <si>
+    <t>Identified this as a classic Check-then-Act concurrency bug. Stressed that synchronization locks (Synchronized/File Lock/Optimistic Lock) are mandatory to make the operation atomic.</t>
+  </si>
+  <si>
+    <t>HALLUCINATION TYPES REFERENCE:</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
     <t>Fabrication</t>
-  </si>
-  <si>
-    <t>AI claimed that Java's standard JDK includes a package named java.nio.file.csv and a class named CSVParser for reading and writing CSV files.</t>
-  </si>
-  <si>
-    <t>There is no package named java.nio.file.csv or class CSVParser in the standard Java SE JDK 17 library.</t>
-  </si>
-  <si>
-    <t>Attempting to import this package caused compile error 'package java.nio.file.csv does not exist'. Verified by searching official Oracle Java SE 17 documentation.</t>
-  </si>
-  <si>
-    <t>Implemented custom parsing logic manually using String.split(",") inside repository subclasses inheriting from generic CsvRepository.</t>
-  </si>
-  <si>
-    <t>Oversimplification</t>
-  </si>
-  <si>
-    <t>AI suggested using Files.writeString(path, content, StandardOpenOption.APPEND) directly in a multi-threaded context and asserted that the OS would automatically queue writes safely without locks.</t>
-  </si>
-  <si>
-    <t>Writing concurrently without locking using APPEND causes interleaved lines, data corruption, and malformed CSV rows.</t>
-  </si>
-  <si>
-    <t>Ran simulation with 100 concurrent threads and inspected the output CSV, finding truncated lines and corrupted headers.</t>
-  </si>
-  <si>
-    <t>Implemented ReentrantReadWriteLock in CsvRepository to ensure only one thread can perform file write operations at a time.</t>
-  </si>
-  <si>
-    <t>Logic Error</t>
-  </si>
-  <si>
-    <t>AI suggested resolving the NO_LOCK race condition by adding a basic if (stock &gt; 0) check before checkout and claimed this made the code thread-safe.</t>
-  </si>
-  <si>
-    <t>A simple if statement is not atomic. Multiple threads can read stock = 1 simultaneously, pass the check, and concurrently subtract stock, causing negative inventory.</t>
-  </si>
-  <si>
-    <t>Ran simulator with 500 threads and observed a final stock of -19 despite having the check in place.</t>
-  </si>
-  <si>
-    <t>Identified this as a classic Check-then-Act concurrency bug. Stressed that synchronization locks (Synchronized/File Lock/Optimistic Lock) are mandatory to make the operation atomic.</t>
-  </si>
-  <si>
-    <t>HALLUCINATION TYPES REFERENCE:</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>Example</t>
   </si>
   <si>
     <t>AI tạo ra thông tin không tồn tại</t>
@@ -546,7 +540,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -628,8 +622,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <i/>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="Cambria"/>
       <family val="1"/>
     </font>
@@ -687,23 +686,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -741,7 +725,32 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1017,22 +1026,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
@@ -1040,7 +1049,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
@@ -1048,7 +1057,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C6" t="s">
@@ -1056,7 +1065,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
@@ -1064,12 +1073,12 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C10">
@@ -1077,105 +1086,105 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="4">
         <f>C11/C10</f>
         <v>0.2</v>
       </c>
-      <c r="E12" s="23" t="s">
-        <v>160</v>
+      <c r="E12" s="27" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="6" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1185,62 +1194,62 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="5" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="7">
+        <v>2</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="7">
         <v>1</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C25" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="12">
+    <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="7">
+        <v>2</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="7">
         <v>1</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="12">
-        <v>2</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="12">
-        <v>1</v>
-      </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="8" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1260,377 +1269,377 @@
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="25" style="14" customWidth="1"/>
-    <col min="5" max="5" width="30" style="14" customWidth="1"/>
-    <col min="6" max="6" width="35" style="14" customWidth="1"/>
-    <col min="7" max="7" width="50" style="14" customWidth="1"/>
+    <col min="4" max="4" width="25" style="9" customWidth="1"/>
+    <col min="5" max="5" width="30" style="9" customWidth="1"/>
+    <col min="6" max="6" width="35" style="9" customWidth="1"/>
+    <col min="7" max="7" width="50" style="9" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11">
+      <c r="A4" s="6">
         <v>1</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11">
+      <c r="A5" s="6">
         <v>2</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11">
+      <c r="A6" s="6">
         <v>3</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
-        <v>4</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11">
-        <v>5</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>81</v>
+      <c r="H8" s="6" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1644,328 +1653,328 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="6" width="30" style="14" customWidth="1"/>
+    <col min="3" max="6" width="30" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+    </row>
+    <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+    </row>
+    <row r="3" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="B3" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F3" s="10" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11">
-        <v>1</v>
-      </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="11" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="100.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="100.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11">
-        <v>2</v>
-      </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="11" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11">
-        <v>4</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="D6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="E6" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="F6" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="11" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="11" t="s">
+    </row>
+    <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-    </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-    </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-    </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-    </row>
-    <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-    </row>
-    <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-    </row>
-    <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-    </row>
-    <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-    </row>
-    <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-    </row>
-    <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-    </row>
-    <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-    </row>
-    <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-    </row>
-    <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-    </row>
-    <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-    </row>
-    <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="6" t="s">
+      <c r="B31" s="10" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="15" t="s">
+      <c r="C31" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B31" s="15" t="s">
+    </row>
+    <row r="32" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="B32" s="6" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" s="11" t="s">
+      <c r="C32" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="11" t="s">
+    </row>
+    <row r="33" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" s="11" t="s">
+      <c r="C33" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="11" t="s">
+    </row>
+    <row r="34" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B34" s="11" t="s">
+      <c r="C34" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="11" t="s">
+    </row>
+    <row r="35" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="s">
+      <c r="B35" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="C35" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="11" t="s">
+    </row>
+    <row r="36" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
+      <c r="B36" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="C36" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1974,7 +1983,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1984,268 +1993,296 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+    </row>
+    <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-    </row>
-    <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+    </row>
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="C5" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="16" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+      <c r="B6" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="C6" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="13"/>
+    </row>
+    <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="B7" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="C7" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="13"/>
+    </row>
+    <row r="8" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="B8" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="13"/>
+    </row>
+    <row r="10" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="13"/>
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="D7" s="18"/>
-    </row>
-    <row r="8" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="18" t="s">
+      <c r="B15" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="B17" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="16" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="18"/>
-    </row>
-    <row r="9" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="B9" s="18" t="s">
+      <c r="B29" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D9" s="18"/>
-    </row>
-    <row r="10" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D10" s="18"/>
-    </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="19" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="21" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D27" s="15" t="s">
+      <c r="B32" s="19" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>159</v>
+      <c r="C32" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
